--- a/data_extactor/batch_10_fa/trimmed/batch_0098_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0098_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | دید نزدیک | توجه شنیداری | دید دور | دقت کنترل | توجه انتخابی | زمان واکنش</t>
+          <t>ترتیب‌دهی اطلاعات | بینایی نزدیک | توجه شنیداری | بینایی دور | دقت کنترل | توجه انتخابی | زمان عکس‌العمل</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ناخداها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای جرثقیل و دکل | اپراتورهای لایروب | کارگران نگهداری و مرمت بزرگراه‌ها | هدایت‌کنندگان قایق‌های موتوری | ملوانان و روغن‌کاران موتورخانه شناورها | نگهبانان و ماموران حراست</t>
+          <t>کاپیتان‌ها، افسران اول و راهنمایان شناورهای دریایی | اپراتورهای جرثقیل و تاورکرین | اپراتورهای لایروب | کارگران راهداری و نگهداری جاده‌ها | قایقرانان قایق‌های موتوری | ملوانان و روغن‌کاران شناورهای دریایی | نگهبانان و ماموران حراست</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال</t>
+          <t>سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | زبان انگلیسی | ترابری و حمل‌ونقل</t>
+          <t>خدمات مشتری و شخصی | زبان انگلیسی | حمل و نقل</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>دید دور | درک شفاهی | بیان شفاهی | دید نزدیک | حساسیت به مسئله | جهت‌یابی فضایی | ادراک عمق</t>
+          <t>بینایی دور | درک شفاهی | بیان شفاهی | بینایی نزدیک | حساسیت به مسئله | جهت‌گیری فضایی | درک عمق</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>باربران هتل و چمدان‌بران | صندوق‌داران | متصدیان باجه و کرایه تجهیزات | متصدیان پذیرش هتل و متل | ماموران اعمال قانون و نظارت بر پارکینگ‌ها | رانندگان سرویس و تشریفات | رانندگان تاکسی</t>
+          <t>متصدیان حمل بار و خدمات هتل | صندوق‌داران | متصدیان باجه و کرایه کالا و خدمات | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | ماموران کنترل و اعمال قانون پارک دوبله و توقف | رانندگان خودروهای سرویس و تشریفات | رانندگان تاکسی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | بازاریابی و فروش | مدیریت و امور اداری | ریاضیات | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | مکانیک | فروش و بازاریابی | مدیریت و اداره | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | دید نزدیک | چابکی دستی | دقت کنترل | استحکام بالاتنه | استقامت بدنی</t>
+          <t>بیان شفاهی | درک شفاهی | بینایی نزدیک | مهارت دستی | دقت کنترل | قدرت تنه | استقامت</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و مکانیک‌های خدمات خودرویی | کارگران شست‌وشوی وسایل نقلیه و تجهیزات | اپراتورهای کمپرسور گاز و ایستگاه‌های پمپاژ گاز | مکانیک‌های تجهیزات موتوری فضای سبز و موتورهای کوچک | اپراتورهای سامانه‌های پمپاژ نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ‌های صنعتی (به‌جز سرچاهی) | آپاراتی‌ها و تعمیرکاران و تعویض‌کنندگان لاستیک</t>
+          <t>مکانیک و تکنسین خدمات خودرو | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | اپراتورهای ایستگاه پمپاژ و کمپرسور گاز | مکانیک موتورهای کوچک و تجهیزات موتوری فضای باز | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای پمپ، به‌جز پمپ‌های سرچاهی | آپاراتی و پنچرگیر و تعویض‌کار لاستیک</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتریان و خدمات فردی | ریاضیات</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | مکانیک | زبان انگلیسی | شیمی | خدمات مشتری و شخصی | ریاضیات</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>سرپرستان جابه‌جایی بار و بارگیری هواپیما | تکنسین‌ها و مکانیک‌های هواپیما | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | کارگران شست‌وشوی وسایل نقلیه و تجهیزات | اپراتورهای تراکتور و لیفتراک‌های صنعتی | کارگران نگهداری و تعمیرات ماشین‌آلات صنعتی | کارگران تعمیرات و نگهداری عمومی تاسیسات</t>
+          <t>سرپرستان بارگیری و جابه‌جایی بار هواپیما | مکانیک و تکنسین خدمات هواپیما | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | شست‌وشوکاران وسایل نقلیه و تجهیزات صنعتی | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | کارگران عمومی تعمیرات و نگهداری تاسیسات</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | ترابری و حمل‌ونقل | رایانه و الکترونیک | مهندسی و فناوری | قوانین و مقررات دولتی | ریاضیات | ساختمان‌سازی و سازه</t>
+          <t>ایمنی و امنیت عمومی | حمل و نقل | رایانه و الکترونیک | مهندسی و فناوری | قانون و دولت | ریاضیات | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | تجسم فضایی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | درک کتبی | استدلال قیاسی | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | نقشه‌برداران ژئودتیک | کارگران نگهداری و مرمت بزرگراه‌ها | تکنسین‌های نقشه‌برداری و نقشه‌کشی | مهندسان حمل‌ونقل و ترافیک | برنامه‌ریزان حمل‌ونقل و ترافیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مهندسان نقشه‌برداری ژئودزی | کارگران راهداری و نگهداری جاده‌ها | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان حمل‌ونقل و ترافیک | برنامه‌ریزان سیستم‌های حمل‌ونقل</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | شنیدن فعال | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی | مدیریت و امور اداری | مکانیک | قوانین و مقررات دولتی</t>
+          <t>حمل و نقل | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | مدیریت و اداره | مکانیک | قانون و دولت</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | درک کتبی | استدلال استقرایی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | درک کتبی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان عملیات فرودگاهی | متصدیان بار و لجستیک کالا | فورواردرها و متصدیان حمل‌ونقل بین‌المللی کالا | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | کارشناسان ایمنی و بهداشت حرفه‌ای | بازرسان تجهیزات، سامانه‌ها و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران ترابری، انبارداری و توزیع</t>
+          <t>کارشناسان عملیات فرودگاهی | کارگزاران حمل‌ونقل و بار | کارشناسان و متصدیان فورواردری و حمل‌ونقل بین‌المللی کالا | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان بهداشت حرفه‌ای و ایمنی کار | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی) | مدیران حمل‌ونقل، انبارداری و توزیع</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | ترابری و حمل‌ونقل | مهندسی و فناوری | قوانین و مقررات دولتی | رایانه و الکترونیک</t>
+          <t>زبان انگلیسی | مکانیک | ایمنی و امنیت عمومی | حمل و نقل | مهندسی و فناوری | قانون و دولت | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | دید نزدیک | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>استدلال استقرایی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>اهمیت بسیار بالای دقت و عدم پذیرش خطا | پیامدهای سنگین ناشی از اشتباه بر ایمنی عمومی | تصمیم‌گیری‌های حساس و قضاوت‌های مستقل | استفاده از تجهیزات حفاظت فردی | مکاتبهٔ ایمیلی | گفت‌وگوی حضوری با همکاران | مواجهه با صداهای با دسی‌بل بالا</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فراوانی تصمیم‌گیری | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | پیامدهای کاری و نتایج سایر کارکنان | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، دارای کنترل شرایط محیطی | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | قرار گرفتن در معرض آلاینده‌ها | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | نامه‌ها و یادداشت‌های کتبی | سطح رقابت | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | صرف زمان برای ایستادن</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا و عملیات هوانوردی | تکنسین‌ها و مکانیک‌های هواپیما | کارشناسان عملیات فرودگاهی | تکنسین‌های اویونیک و الکترونیک هواپیما | خلبانان تجاری | کارشناسان ایمنی و بهداشت حرفه‌ای | بازرسان ترابری و حمل‌ونقل</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مکانیک و تکنسین خدمات هواپیما | کارشناسان عملیات فرودگاهی | تکنسین‌های اویونیک و الکترونیک پرواز | خلبانان تجاری | کارشناسان بهداشت حرفه‌ای و ایمنی کار | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
+          <t>گوش دادن فعال | تفکر انتقادی | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مکانیک | ترابری و حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی</t>
+          <t>مکانیک | حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری در بستن الگو | استدلال قیاسی | توجه انتخابی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | درک شفاهی | ثبات دست و بازو | انعطاف‌پذیری بستار | استدلال قیاسی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرویی | مکانیک‌های اتوبوس، کامیون و متخصصان موتورهای دیزلی | کاردان‌ها و تکنسین‌های کالیبراسیون | بازرسان، آزمون‌گران، تفکیک‌کنندگان، نمونه‌برداران و متصدیان توزین | کارشناسان ایمنی و بهداشت حرفه‌ای | بازرسان ترابری و حمل‌ونقل</t>
+          <t>تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | مکانیک اتوبوس و کامیون و متخصص موتورهای دیزلی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | کارشناسان بهداشت حرفه‌ای و ایمنی کار | بازرسان ترابری و حمل‌ونقل</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>نرم‌افزار زمان‌بندی و نوبت‌دهی | نرم‌افزار ثبت ساعت کاری | نرم‌افزار Microsoft Word | نرم‌افزار Microsoft Office | نرم‌افزار Microsoft Windows | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار زمان‌بندی قرار ملاقات | نرم‌افزار ایمیل | نرم‌افزار Microsoft Office | Microsoft Windows | نرم‌افزار Microsoft Windows</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | نظارت | درک مطلب</t>
+          <t>سخن گفتن | گوش دادن فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی</t>
+          <t>حمل و نقل | زبان انگلیسی | ایمنی و امنیت عمومی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>رانندگان اتوبوس‌های شهری و بین‌شهری | سرپرستان رده‌اول مهمانداران و متصدیان خدمات مسافران | مهمانداران هواپیما | متصدیان پذیرش هتل و متل | رئیسان قطار و سرپرستان ایستگاه راه‌آهن | متصدیان فروش و رزرو بلیت و خدمات سفر | راهنمایان سالن، متصدیان لابی و کنترل‌کنندگان بلیت</t>
+          <t>رانندگان اتوبوس‌های درون‌شهری و برون‌شهری | سرپرستان رده‌اول مهمانداران و خدمه مسافری | مهمانداران هواپیما | متصدیان پذیرش هتل‌ها، متل‌ها و مراکز اقامتی | رؤسای قطار و مدیران محوطه راه‌آهن | متصدیان فروش بلیت، رزرواسیون و خدمات سفر | راهنماها، متصدیان سالن و بلیط‌گیرها</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>نظارت | شنیدن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
+          <t>نظارت | گوش دادن فعال | تفکر انتقادی | درک مطلب | سخن گفتن</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>ترابری و حمل‌ونقل | ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مکانیک | جغرافیا</t>
+          <t>حمل و نقل | ایمنی و امنیت عمومی | خدمات مشتری و شخصی | زبان انگلیسی | مکانیک | جغرافیا</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | هماهنگی اندام‌ها | دقت کنترل | قدرت ایستا | دید نزدیک</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | هماهنگی چند عضو | دقت کنترل | قدرت ایستا | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متصدیان خدمات و سوخت‌رسانی فرودگاهی | متصدیان پارکینگ | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | مهمانداران و متصدیان خدمات مسافران | اپراتورهای تراکتور و لیفتراک‌های صنعتی | کارگران ساده و جابه‌جایی بار، کالا و بسته‌ها | اعزام‌کنندگان و دیسپچرهای ترابری (به‌جز پلیس، آتش‌نشانی و اورژانس)</t>
+          <t>متصدیان خدمات زمینی و سوخت‌رسانی فرودگاهی | متصدیان پارکینگ | متصدیان جایگاه‌های سوخت و خدمات وسایل نقلیه و شناورها | مهمانداران و متصدیان خدمات مسافران | رانندگان و اپراتورهای تراکتور و لیفتراک صنعتی | کارگران جابه‌جایی دستی بار، کالا و مصالح | متصدیان دیسپاچ و اعزام</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
